--- a/artfynd/A 18392-2026 artfynd.xlsx
+++ b/artfynd/A 18392-2026 artfynd.xlsx
@@ -1122,57 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133889183</v>
+        <v>133889172</v>
       </c>
       <c r="B6" t="n">
-        <v>99181</v>
+        <v>79117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620821</v>
+        <v>620777</v>
       </c>
       <c r="R6" t="n">
-        <v>7024191</v>
+        <v>7024042</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1204,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1211,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1368,45 +1355,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133889172</v>
+        <v>133889183</v>
       </c>
       <c r="B8" t="n">
-        <v>79117</v>
+        <v>99181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620777</v>
+        <v>620821</v>
       </c>
       <c r="R8" t="n">
-        <v>7024042</v>
+        <v>7024191</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1438,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,6 +1456,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1582,45 +1582,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133889171</v>
+        <v>133889170</v>
       </c>
       <c r="B10" t="n">
-        <v>91960</v>
+        <v>99181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620749</v>
+        <v>620739</v>
       </c>
       <c r="R10" t="n">
-        <v>7024066</v>
+        <v>7024103</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1652,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,6 +1683,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1689,57 +1702,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133889170</v>
+        <v>133889171</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>91960</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620739</v>
+        <v>620749</v>
       </c>
       <c r="R11" t="n">
-        <v>7024103</v>
+        <v>7024066</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1771,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,7 +1791,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133889182</v>
+        <v>133889175</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620775</v>
+        <v>620719</v>
       </c>
       <c r="R12" t="n">
-        <v>7024174</v>
+        <v>7024010</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133889175</v>
+        <v>133889182</v>
       </c>
       <c r="B13" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620719</v>
+        <v>620775</v>
       </c>
       <c r="R13" t="n">
-        <v>7024010</v>
+        <v>7024174</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,17 +2033,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133889166</v>
+        <v>133889180</v>
       </c>
       <c r="B15" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,34 +2179,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620858</v>
+        <v>620745</v>
       </c>
       <c r="R15" t="n">
-        <v>7024158</v>
+        <v>7024152</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2238,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,8 +2260,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2401,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133889180</v>
+        <v>133889166</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,37 +2431,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620745</v>
+        <v>620858</v>
       </c>
       <c r="R17" t="n">
-        <v>7024152</v>
+        <v>7024158</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2474,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,24 +2509,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -3006,32 +3006,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133889181</v>
+        <v>133889164</v>
       </c>
       <c r="B22" t="n">
-        <v>91960</v>
+        <v>92392</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620776</v>
+        <v>620859</v>
       </c>
       <c r="R22" t="n">
         <v>7024165</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133889164</v>
+        <v>133889181</v>
       </c>
       <c r="B23" t="n">
-        <v>92392</v>
+        <v>91960</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620859</v>
+        <v>620776</v>
       </c>
       <c r="R23" t="n">
         <v>7024165</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18392-2026 artfynd.xlsx
+++ b/artfynd/A 18392-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133902541</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133902542</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133889169</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>133889167</v>
       </c>
       <c r="B5" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,45 +1122,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133889172</v>
+        <v>133889183</v>
       </c>
       <c r="B6" t="n">
-        <v>79117</v>
+        <v>99188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620777</v>
+        <v>620821</v>
       </c>
       <c r="R6" t="n">
-        <v>7024042</v>
+        <v>7024191</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1192,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,6 +1223,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,7 +1245,7 @@
         <v>133889176</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,57 +1368,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133889183</v>
+        <v>133889172</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620821</v>
+        <v>620777</v>
       </c>
       <c r="R8" t="n">
-        <v>7024191</v>
+        <v>7024042</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1437,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1457,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>133889168</v>
       </c>
       <c r="B9" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,57 +1582,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133889170</v>
+        <v>133889171</v>
       </c>
       <c r="B10" t="n">
-        <v>99181</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620739</v>
+        <v>620749</v>
       </c>
       <c r="R10" t="n">
-        <v>7024103</v>
+        <v>7024066</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1664,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1671,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1702,45 +1689,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133889171</v>
+        <v>133889170</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620749</v>
+        <v>620739</v>
       </c>
       <c r="R11" t="n">
-        <v>7024066</v>
+        <v>7024103</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1772,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,6 +1790,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133889175</v>
+        <v>133889182</v>
       </c>
       <c r="B12" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620719</v>
+        <v>620775</v>
       </c>
       <c r="R12" t="n">
-        <v>7024010</v>
+        <v>7024174</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133889182</v>
+        <v>133889175</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620775</v>
+        <v>620719</v>
       </c>
       <c r="R13" t="n">
-        <v>7024174</v>
+        <v>7024010</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,17 +2033,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
         <v>133889174</v>
       </c>
       <c r="B14" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133889180</v>
+        <v>133889166</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,37 +2179,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620745</v>
+        <v>620858</v>
       </c>
       <c r="R15" t="n">
-        <v>7024152</v>
+        <v>7024158</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2241,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,24 +2257,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2297,7 +2278,7 @@
         <v>133889161</v>
       </c>
       <c r="B16" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133889166</v>
+        <v>133889180</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,34 +2412,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620858</v>
+        <v>620745</v>
       </c>
       <c r="R17" t="n">
-        <v>7024158</v>
+        <v>7024152</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2490,7 +2474,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2484,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,8 +2493,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2530,7 +2530,7 @@
         <v>133889179</v>
       </c>
       <c r="B18" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>133889163</v>
       </c>
       <c r="B19" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>133889177</v>
       </c>
       <c r="B20" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>133889173</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,32 +3006,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133889164</v>
+        <v>133889181</v>
       </c>
       <c r="B22" t="n">
-        <v>92392</v>
+        <v>91967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620859</v>
+        <v>620776</v>
       </c>
       <c r="R22" t="n">
         <v>7024165</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133889181</v>
+        <v>133889164</v>
       </c>
       <c r="B23" t="n">
-        <v>91960</v>
+        <v>92399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620776</v>
+        <v>620859</v>
       </c>
       <c r="R23" t="n">
         <v>7024165</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,7 +3223,7 @@
         <v>133889178</v>
       </c>
       <c r="B24" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18392-2026 artfynd.xlsx
+++ b/artfynd/A 18392-2026 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133902541</v>
+        <v>133889167</v>
       </c>
       <c r="B2" t="n">
-        <v>98053</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillsjötjärn, Ång</t>
+          <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620813</v>
+        <v>620860</v>
       </c>
       <c r="R2" t="n">
-        <v>7024209</v>
+        <v>7024157</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133902542</v>
+        <v>133889174</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillsjötjärn, Ång</t>
+          <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620908</v>
+        <v>620734</v>
       </c>
       <c r="R3" t="n">
-        <v>7024150</v>
+        <v>7024003</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133889169</v>
+        <v>133889166</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620909</v>
+        <v>620858</v>
       </c>
       <c r="R4" t="n">
-        <v>7024136</v>
+        <v>7024158</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -962,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,24 +978,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1015,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133889167</v>
+        <v>133889168</v>
       </c>
       <c r="B5" t="n">
-        <v>92238</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620860</v>
+        <v>620891</v>
       </c>
       <c r="R5" t="n">
-        <v>7024157</v>
+        <v>7024163</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,57 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133889183</v>
+        <v>133889171</v>
       </c>
       <c r="B6" t="n">
-        <v>99188</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620821</v>
+        <v>620749</v>
       </c>
       <c r="R6" t="n">
-        <v>7024191</v>
+        <v>7024066</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1204,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1192,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133889176</v>
+        <v>133889181</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,37 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620719</v>
+        <v>620776</v>
       </c>
       <c r="R7" t="n">
-        <v>7024021</v>
+        <v>7024165</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1315,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,24 +1299,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1368,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133889172</v>
+        <v>133889164</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>92406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1403,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620777</v>
+        <v>620859</v>
       </c>
       <c r="R8" t="n">
-        <v>7024042</v>
+        <v>7024165</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1438,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,48 +1424,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133889168</v>
+        <v>133889169</v>
       </c>
       <c r="B9" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620891</v>
+        <v>620909</v>
       </c>
       <c r="R9" t="n">
-        <v>7024163</v>
+        <v>7024136</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1497,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1507,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,8 +1516,24 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1582,45 +1550,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133889171</v>
+        <v>133889173</v>
       </c>
       <c r="B10" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620749</v>
+        <v>620760</v>
       </c>
       <c r="R10" t="n">
-        <v>7024066</v>
+        <v>7024033</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1652,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,8 +1642,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1689,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133889170</v>
+        <v>133889176</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,35 +1687,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1736,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620739</v>
+        <v>620719</v>
       </c>
       <c r="R11" t="n">
-        <v>7024103</v>
+        <v>7024021</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1771,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,6 +1771,21 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1809,14 +1802,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133889182</v>
+        <v>133889180</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1847,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620775</v>
+        <v>620745</v>
       </c>
       <c r="R12" t="n">
-        <v>7024174</v>
+        <v>7024152</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1882,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,17 +1900,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1935,32 +1928,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133889175</v>
+        <v>133889182</v>
       </c>
       <c r="B13" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620719</v>
+        <v>620775</v>
       </c>
       <c r="R13" t="n">
-        <v>7024010</v>
+        <v>7024174</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2008,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,17 +2026,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2061,48 +2054,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133889174</v>
+        <v>133902542</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilsjötjärn, Ång</t>
+          <t>Lillsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620734</v>
+        <v>620908</v>
       </c>
       <c r="R14" t="n">
-        <v>7024003</v>
+        <v>7024150</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,22 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133889166</v>
+        <v>133889163</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,34 +2172,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620858</v>
+        <v>620842</v>
       </c>
       <c r="R15" t="n">
-        <v>7024158</v>
+        <v>7024165</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2238,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,8 +2253,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2275,32 +2287,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133889161</v>
+        <v>133889175</v>
       </c>
       <c r="B16" t="n">
-        <v>80486</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,13 +2325,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620810</v>
+        <v>620719</v>
       </c>
       <c r="R16" t="n">
-        <v>7024196</v>
+        <v>7024010</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2348,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133889180</v>
+        <v>133889178</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,21 +2424,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2439,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620745</v>
+        <v>620732</v>
       </c>
       <c r="R17" t="n">
-        <v>7024152</v>
+        <v>7024032</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2474,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,17 +2511,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2527,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133889179</v>
+        <v>133889161</v>
       </c>
       <c r="B18" t="n">
-        <v>98053</v>
+        <v>80493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,37 +2550,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620738</v>
+        <v>620810</v>
       </c>
       <c r="R18" t="n">
-        <v>7024152</v>
+        <v>7024196</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2597,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2622,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,8 +2631,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2634,37 +2665,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133889163</v>
+        <v>133889170</v>
       </c>
       <c r="B19" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2672,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620842</v>
+        <v>620739</v>
       </c>
       <c r="R19" t="n">
-        <v>7024165</v>
+        <v>7024103</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2707,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2757,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,21 +2769,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2763,7 +2788,7 @@
         <v>133889177</v>
       </c>
       <c r="B20" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2880,37 +2905,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133889173</v>
+        <v>133889183</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2918,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620760</v>
+        <v>620821</v>
       </c>
       <c r="R21" t="n">
-        <v>7024033</v>
+        <v>7024191</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2953,7 +2987,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2963,7 +2997,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,21 +3009,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3006,32 +3025,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133889181</v>
+        <v>133889179</v>
       </c>
       <c r="B22" t="n">
-        <v>91967</v>
+        <v>98060</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3041,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620776</v>
+        <v>620738</v>
       </c>
       <c r="R22" t="n">
-        <v>7024165</v>
+        <v>7024152</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3076,7 +3095,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3086,7 +3105,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,48 +3132,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133889164</v>
+        <v>133902541</v>
       </c>
       <c r="B23" t="n">
-        <v>92399</v>
+        <v>98060</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilsjötjärn, Ång</t>
+          <t>Lillsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620859</v>
+        <v>620813</v>
       </c>
       <c r="R23" t="n">
-        <v>7024165</v>
+        <v>7024209</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3183,7 +3202,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3212,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,22 +3227,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133889178</v>
+        <v>133889172</v>
       </c>
       <c r="B24" t="n">
-        <v>80481</v>
+        <v>79131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,40 +3250,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lilsjötjärn, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620732</v>
+        <v>620777</v>
       </c>
       <c r="R24" t="n">
-        <v>7024032</v>
+        <v>7024042</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3293,7 +3309,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3303,7 +3319,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,24 +3328,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 18392-2026 artfynd.xlsx
+++ b/artfynd/A 18392-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889174</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889166</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889181</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889164</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889169</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889173</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889176</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1925,6 +1980,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889180</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889182</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2158,6 +2223,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133902542</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2284,6 +2354,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889163</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889175</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2536,6 +2616,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889178</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2662,6 +2747,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889161</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2782,6 +2872,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889170</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2902,6 +2997,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889177</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3022,6 +3122,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889183</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3129,6 +3234,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889179</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3236,6 +3346,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133902541</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3343,8 +3458,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>